--- a/Form Trace/就職作品の仕様書.xlsx
+++ b/Form Trace/就職作品の仕様書.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Downloads\ソロゲーム制作\GameEmployment\Form Trace\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24B6DE20-10D0-4346-A750-2B313FC8CE2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E0A2723-D3FA-4524-898D-9A145738CD9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{20A4CC97-BA0B-4592-A6EC-2FCEFFB1D2AE}"/>
+    <workbookView xWindow="5535" yWindow="-14445" windowWidth="21090" windowHeight="13515" activeTab="5" xr2:uid="{20A4CC97-BA0B-4592-A6EC-2FCEFFB1D2AE}"/>
   </bookViews>
   <sheets>
     <sheet name="0.目次" sheetId="1" r:id="rId1"/>
@@ -1355,14 +1355,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>とびかかる
-回転</t>
-    <rPh sb="6" eb="8">
-      <t>カイテン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>※HPと攻撃力はあとから変更する可能性が高いので目安程度に</t>
     <rPh sb="4" eb="7">
       <t>コウゲキリョク</t>
@@ -1524,6 +1516,23 @@
     </rPh>
     <rPh sb="11" eb="13">
       <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>前方に広範囲の斬撃
+回転</t>
+    <rPh sb="0" eb="2">
+      <t>ゼンポウ</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>コウハンイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ザンゲキ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>カイテン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2820,26 +2829,26 @@
     <row r="19" spans="2:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="20" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B20" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C20" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="C20" s="4" t="s">
-        <v>152</v>
-      </c>
       <c r="D20" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="E20" s="4" t="s">
         <v>155</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>156</v>
       </c>
       <c r="F20" s="5"/>
     </row>
     <row r="21" spans="2:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B21" s="6"/>
       <c r="C21" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="D21" s="7" t="s">
         <v>153</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>154</v>
       </c>
       <c r="E21" s="7"/>
       <c r="F21" s="8"/>
@@ -3504,7 +3513,7 @@
     </row>
     <row r="9" spans="1:5" ht="37.5" x14ac:dyDescent="0.4">
       <c r="B9" s="27" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C9" s="2">
         <v>100</v>
@@ -3513,12 +3522,12 @@
         <v>20</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="56.25" x14ac:dyDescent="0.4">
       <c r="B10" s="29" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C10" s="2">
         <v>150</v>
@@ -3527,12 +3536,12 @@
         <v>20</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="37.5" x14ac:dyDescent="0.4">
       <c r="B11" s="29" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C11" s="2">
         <v>700</v>
@@ -3541,16 +3550,17 @@
         <v>30</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B12" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Form Trace/就職作品の仕様書.xlsx
+++ b/Form Trace/就職作品の仕様書.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Downloads\ソロゲーム制作\GameEmployment\Form Trace\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC_User\Downloads\個人製作\GameEmployment\Form Trace\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E0A2723-D3FA-4524-898D-9A145738CD9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69CEBE4E-1C3D-4194-8E5F-098E516E209B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5535" yWindow="-14445" windowWidth="21090" windowHeight="13515" activeTab="5" xr2:uid="{20A4CC97-BA0B-4592-A6EC-2FCEFFB1D2AE}"/>
+    <workbookView xWindow="-2370" yWindow="435" windowWidth="12675" windowHeight="14535" firstSheet="4" activeTab="5" xr2:uid="{20A4CC97-BA0B-4592-A6EC-2FCEFFB1D2AE}"/>
   </bookViews>
   <sheets>
     <sheet name="0.目次" sheetId="1" r:id="rId1"/>
@@ -34,9 +34,6 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
@@ -1395,23 +1392,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>腕部による薙ぎ払い
-ビームとか打つ？</t>
-    <rPh sb="0" eb="2">
-      <t>ワンブ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>ナ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>ハラ</t>
-    </rPh>
-    <rPh sb="15" eb="16">
-      <t>ウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>火の玉を飛ばす
 ブレス的なものor
 前方に弾をいっぱい出す</t>
@@ -1533,6 +1513,39 @@
     </rPh>
     <rPh sb="10" eb="12">
       <t>カイテン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">腕部による薙ぎ払い
+叩きつける攻撃
+パンチ
+キック
+両腕部でクロスさせながら殴る攻撃
+</t>
+    <rPh sb="0" eb="2">
+      <t>ワンブ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ナ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ハラ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>タタ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="26" eb="29">
+      <t>リョウワンブ</t>
+    </rPh>
+    <rPh sb="38" eb="39">
+      <t>ナグ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>コウゲキ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1760,7 +1773,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1803,22 +1816,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1837,15 +1841,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2304,9 +2299,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2344,7 +2339,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2450,7 +2445,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2592,7 +2587,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2713,10 +2708,10 @@
       <c r="C7" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="15" t="s">
+      <c r="D7" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="E7" s="15" t="s">
+      <c r="E7" s="14" t="s">
         <v>19</v>
       </c>
       <c r="F7" s="5" t="s">
@@ -2725,7 +2720,7 @@
     </row>
     <row r="8" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B8" s="6"/>
-      <c r="C8" s="16" t="s">
+      <c r="C8" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D8" s="7" t="s">
@@ -2771,7 +2766,7 @@
       <c r="F14" s="5"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="B15" s="17"/>
+      <c r="B15" s="15"/>
       <c r="C15" s="2" t="s">
         <v>39</v>
       </c>
@@ -2781,27 +2776,27 @@
       <c r="E15" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F15" s="18" t="s">
+      <c r="F15" s="16" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="B16" s="17"/>
-      <c r="C16" s="14" t="s">
+      <c r="B16" s="15"/>
+      <c r="C16" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="D16" s="14" t="s">
+      <c r="D16" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E16" s="14" t="s">
+      <c r="E16" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="F16" s="19" t="s">
+      <c r="F16" s="16" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B17" s="17"/>
+      <c r="B17" s="15"/>
       <c r="C17" s="2" t="s">
         <v>32</v>
       </c>
@@ -2811,7 +2806,7 @@
       <c r="E17" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F17" s="18"/>
+      <c r="F17" s="16"/>
     </row>
     <row r="18" spans="2:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B18" s="6"/>
@@ -2829,26 +2824,26 @@
     <row r="19" spans="2:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="20" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B20" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C20" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="C20" s="4" t="s">
-        <v>151</v>
-      </c>
       <c r="D20" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="E20" s="4" t="s">
         <v>154</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>155</v>
       </c>
       <c r="F20" s="5"/>
     </row>
     <row r="21" spans="2:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B21" s="6"/>
       <c r="C21" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="D21" s="7" t="s">
         <v>152</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>153</v>
       </c>
       <c r="E21" s="7"/>
       <c r="F21" s="8"/>
@@ -2867,7 +2862,7 @@
       <c r="E23" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="F23" s="20" t="s">
+      <c r="F23" s="17" t="s">
         <v>48</v>
       </c>
     </row>
@@ -3022,94 +3017,94 @@
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="C3" s="22" t="s">
+      <c r="C3" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="D3" s="23" t="s">
+      <c r="D3" s="20" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="B4" s="24" t="s">
+      <c r="B4" s="21" t="s">
         <v>76</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="D4" s="18"/>
+      <c r="D4" s="16"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="B5" s="24" t="s">
+      <c r="B5" s="21" t="s">
         <v>78</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="D5" s="18" t="s">
+      <c r="D5" s="16" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="21" t="s">
         <v>82</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="D6" s="18" t="s">
+      <c r="D6" s="16" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="B7" s="24" t="s">
+      <c r="B7" s="21" t="s">
         <v>85</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="D7" s="18"/>
+      <c r="D7" s="16"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="B8" s="24" t="s">
+      <c r="B8" s="21" t="s">
         <v>87</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D8" s="18"/>
+      <c r="D8" s="16"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="B9" s="24" t="s">
+      <c r="B9" s="21" t="s">
         <v>89</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D9" s="18"/>
+      <c r="D9" s="16"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="B10" s="24" t="s">
+      <c r="B10" s="21" t="s">
         <v>90</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D10" s="18"/>
+      <c r="D10" s="16"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="B11" s="24" t="s">
+      <c r="B11" s="21" t="s">
         <v>94</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D11" s="18"/>
+      <c r="D11" s="16"/>
     </row>
     <row r="12" spans="1:4" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B12" s="25" t="s">
+      <c r="B12" s="22" t="s">
         <v>93</v>
       </c>
       <c r="C12" s="7" t="s">
@@ -3123,90 +3118,90 @@
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="B15" s="21" t="s">
+      <c r="B15" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="C15" s="22" t="s">
+      <c r="C15" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="D15" s="23" t="s">
+      <c r="D15" s="20" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="B16" s="24" t="s">
+      <c r="B16" s="21" t="s">
         <v>76</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="D16" s="18"/>
+      <c r="D16" s="16"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="B17" s="24" t="s">
+      <c r="B17" s="21" t="s">
         <v>78</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="D17" s="18" t="s">
+      <c r="D17" s="16" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="B18" s="24" t="s">
+      <c r="B18" s="21" t="s">
         <v>82</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="D18" s="18" t="s">
+      <c r="D18" s="16" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="B19" s="24" t="s">
+      <c r="B19" s="21" t="s">
         <v>85</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="D19" s="18" t="s">
+      <c r="D19" s="16" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="B20" s="24" t="s">
+      <c r="B20" s="21" t="s">
         <v>100</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="D20" s="18"/>
+      <c r="D20" s="16"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="B21" s="24" t="s">
+      <c r="B21" s="21" t="s">
         <v>89</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="D21" s="18"/>
+      <c r="D21" s="16"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="B22" s="24" t="s">
+      <c r="B22" s="21" t="s">
         <v>90</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="D22" s="18"/>
+      <c r="D22" s="16"/>
     </row>
     <row r="23" spans="1:4" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B23" s="28" t="s">
+      <c r="B23" s="22" t="s">
         <v>115</v>
       </c>
-      <c r="C23" s="16" t="s">
+      <c r="C23" s="7" t="s">
         <v>116</v>
       </c>
       <c r="D23" s="8"/>
@@ -3215,10 +3210,10 @@
       <c r="A25" t="s">
         <v>102</v>
       </c>
-      <c r="B25" s="26"/>
+      <c r="B25" s="1"/>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="B26" s="27" t="s">
+      <c r="B26" s="23" t="s">
         <v>107</v>
       </c>
       <c r="C26" s="2" t="s">
@@ -3229,7 +3224,7 @@
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="B27" s="27" t="s">
+      <c r="B27" s="23" t="s">
         <v>103</v>
       </c>
       <c r="C27" s="2" t="s">
@@ -3240,7 +3235,7 @@
       </c>
     </row>
     <row r="28" spans="1:4" ht="56.25" x14ac:dyDescent="0.4">
-      <c r="B28" s="27" t="s">
+      <c r="B28" s="23" t="s">
         <v>105</v>
       </c>
       <c r="C28" s="9" t="s">
@@ -3251,7 +3246,7 @@
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="B29" s="29" t="s">
+      <c r="B29" s="23" t="s">
         <v>134</v>
       </c>
       <c r="C29" s="2" t="s">
@@ -3267,7 +3262,7 @@
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="B32" s="27" t="s">
+      <c r="B32" s="23" t="s">
         <v>107</v>
       </c>
       <c r="C32" s="2" t="s">
@@ -3278,7 +3273,7 @@
       </c>
     </row>
     <row r="33" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B33" s="27" t="s">
+      <c r="B33" s="23" t="s">
         <v>103</v>
       </c>
       <c r="C33" s="2">
@@ -3289,7 +3284,7 @@
       </c>
     </row>
     <row r="34" spans="2:4" ht="56.25" x14ac:dyDescent="0.4">
-      <c r="B34" s="27" t="s">
+      <c r="B34" s="23" t="s">
         <v>105</v>
       </c>
       <c r="C34" s="9">
@@ -3300,7 +3295,7 @@
       </c>
     </row>
     <row r="35" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B35" s="29" t="s">
+      <c r="B35" s="23" t="s">
         <v>134</v>
       </c>
       <c r="C35" s="2">
@@ -3453,42 +3448,42 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="C2" s="22" t="s">
+      <c r="C2" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="D2" s="23" t="s">
+      <c r="D2" s="20" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="21" t="s">
         <v>103</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="D3" s="30" t="s">
+      <c r="D3" s="24" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="B4" s="24" t="s">
+      <c r="B4" s="21" t="s">
         <v>134</v>
       </c>
       <c r="C4" s="2"/>
-      <c r="D4" s="18"/>
+      <c r="D4" s="16"/>
     </row>
     <row r="5" spans="1:5" ht="57" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B5" s="25" t="s">
+      <c r="B5" s="22" t="s">
         <v>140</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="D5" s="31" t="s">
+      <c r="D5" s="25" t="s">
         <v>141</v>
       </c>
     </row>
@@ -3498,7 +3493,7 @@
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="B8" s="29" t="s">
+      <c r="B8" s="23" t="s">
         <v>139</v>
       </c>
       <c r="C8" s="2" t="s">
@@ -3512,7 +3507,7 @@
       </c>
     </row>
     <row r="9" spans="1:5" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="B9" s="27" t="s">
+      <c r="B9" s="23" t="s">
         <v>145</v>
       </c>
       <c r="C9" s="2">
@@ -3522,11 +3517,11 @@
         <v>20</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="56.25" x14ac:dyDescent="0.4">
-      <c r="B10" s="29" t="s">
+      <c r="B10" s="23" t="s">
         <v>146</v>
       </c>
       <c r="C10" s="2">
@@ -3536,11 +3531,11 @@
         <v>20</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="B11" s="29" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="131.25" x14ac:dyDescent="0.4">
+      <c r="B11" s="23" t="s">
         <v>147</v>
       </c>
       <c r="C11" s="2">
@@ -3550,7 +3545,7 @@
         <v>30</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.4">

--- a/Form Trace/就職作品の仕様書.xlsx
+++ b/Form Trace/就職作品の仕様書.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC_User\Downloads\個人製作\GameEmployment\Form Trace\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Downloads\ソロゲーム制作\GameEmployment\Form Trace\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69CEBE4E-1C3D-4194-8E5F-098E516E209B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01B7243E-C410-4AF6-BF05-3BF4C8F0414A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-2370" yWindow="435" windowWidth="12675" windowHeight="14535" firstSheet="4" activeTab="5" xr2:uid="{20A4CC97-BA0B-4592-A6EC-2FCEFFB1D2AE}"/>
+    <workbookView xWindow="11040" yWindow="3225" windowWidth="14610" windowHeight="9300" firstSheet="1" activeTab="4" xr2:uid="{20A4CC97-BA0B-4592-A6EC-2FCEFFB1D2AE}"/>
   </bookViews>
   <sheets>
     <sheet name="0.目次" sheetId="1" r:id="rId1"/>
@@ -34,12 +34,15 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="158">
   <si>
     <t>目次</t>
     <rPh sb="0" eb="2">
@@ -1546,6 +1549,28 @@
     </rPh>
     <rPh sb="40" eb="42">
       <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵を倒すだけでなく敵を倒す以外のクエストを作ってもいいかもね</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>タオ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>タオ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>イガイ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ツク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2299,9 +2324,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2339,7 +2364,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2445,7 +2470,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2587,7 +2612,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -3313,7 +3338,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0302D8A9-2651-4550-B723-7AEB3FF4C0F4}">
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -3422,6 +3447,11 @@
     <row r="18" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B18" t="s">
         <v>131</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B21" t="s">
+        <v>157</v>
       </c>
     </row>
   </sheetData>
